--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,42 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R5" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B6" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1133,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R6" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B5" t="n">
-        <v>79031</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1026,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R5" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>79031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,42 +1143,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R6" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128372905</v>
+        <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>91380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440639</v>
+        <v>440580</v>
       </c>
       <c r="R2" t="n">
-        <v>6763304</v>
+        <v>6763336</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack. Gamla</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373388</v>
+        <v>128372905</v>
       </c>
       <c r="B3" t="n">
-        <v>91375</v>
+        <v>57673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440580</v>
+        <v>440639</v>
       </c>
       <c r="R3" t="n">
-        <v>6763336</v>
+        <v>6763304</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack. Gamla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98473</v>
+        <v>98478</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>128372838</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>91380</v>
+        <v>91472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128372905</v>
       </c>
       <c r="B3" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1026,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R5" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B6" t="n">
-        <v>57673</v>
+        <v>79083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,42 +1143,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R6" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>79083</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,42 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R5" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B6" t="n">
-        <v>79083</v>
+        <v>57685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1133,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R6" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128372905</v>
       </c>
       <c r="B3" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>128372838</v>
       </c>
       <c r="B6" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373388</v>
+        <v>128372905</v>
       </c>
       <c r="B2" t="n">
-        <v>91486</v>
+        <v>57689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440580</v>
+        <v>440639</v>
       </c>
       <c r="R2" t="n">
-        <v>6763336</v>
+        <v>6763304</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack. Gamla</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128372905</v>
+        <v>128373388</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>91486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440639</v>
+        <v>440580</v>
       </c>
       <c r="R3" t="n">
-        <v>6763304</v>
+        <v>6763336</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack. Gamla</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1026,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R5" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,42 +1143,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R6" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128372905</v>
+        <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>57689</v>
+        <v>91487</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440639</v>
+        <v>440580</v>
       </c>
       <c r="R2" t="n">
-        <v>6763304</v>
+        <v>6763336</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack. Gamla</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373388</v>
+        <v>128372905</v>
       </c>
       <c r="B3" t="n">
-        <v>91486</v>
+        <v>57689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440580</v>
+        <v>440639</v>
       </c>
       <c r="R3" t="n">
-        <v>6763336</v>
+        <v>6763304</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack. Gamla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,42 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R5" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B6" t="n">
-        <v>79089</v>
+        <v>57689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1133,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R6" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128372905</v>
       </c>
       <c r="B3" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1026,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R5" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B6" t="n">
-        <v>57689</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,42 +1143,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R6" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,42 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R5" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B6" t="n">
-        <v>79116</v>
+        <v>57716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1133,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R6" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373388</v>
+        <v>128372905</v>
       </c>
       <c r="B2" t="n">
-        <v>91524</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440580</v>
+        <v>440639</v>
       </c>
       <c r="R2" t="n">
-        <v>6763336</v>
+        <v>6763304</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack. Gamla</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128372905</v>
+        <v>128373388</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>91524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440639</v>
+        <v>440580</v>
       </c>
       <c r="R3" t="n">
-        <v>6763304</v>
+        <v>6763336</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack. Gamla</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1026,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R5" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1090,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1100,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,42 +1143,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R6" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128372905</v>
+        <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>91528</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440639</v>
+        <v>440580</v>
       </c>
       <c r="R2" t="n">
-        <v>6763304</v>
+        <v>6763336</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack. Gamla</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373388</v>
+        <v>128372905</v>
       </c>
       <c r="B3" t="n">
-        <v>91524</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440580</v>
+        <v>440639</v>
       </c>
       <c r="R3" t="n">
-        <v>6763336</v>
+        <v>6763304</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack. Gamla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128372838</v>
+        <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,42 +1026,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440534</v>
+        <v>440620</v>
       </c>
       <c r="R5" t="n">
-        <v>6763273</v>
+        <v>6763308</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,12 +1095,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128373425</v>
+        <v>128372838</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>57720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,37 +1133,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440620</v>
+        <v>440534</v>
       </c>
       <c r="R6" t="n">
-        <v>6763308</v>
+        <v>6763273</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1197,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,7 +1207,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128373388</v>
+        <v>128372905</v>
       </c>
       <c r="B2" t="n">
-        <v>91528</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440580</v>
+        <v>440639</v>
       </c>
       <c r="R2" t="n">
-        <v>6763336</v>
+        <v>6763304</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack. Gamla</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128372905</v>
+        <v>128373388</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>91528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440639</v>
+        <v>440580</v>
       </c>
       <c r="R3" t="n">
-        <v>6763304</v>
+        <v>6763336</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack. Gamla</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128372905</v>
+        <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>91533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>440639</v>
+        <v>440580</v>
       </c>
       <c r="R2" t="n">
-        <v>6763304</v>
+        <v>6763336</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack. Gamla</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128373388</v>
+        <v>128372905</v>
       </c>
       <c r="B3" t="n">
-        <v>91528</v>
+        <v>57723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440580</v>
+        <v>440639</v>
       </c>
       <c r="R3" t="n">
-        <v>6763336</v>
+        <v>6763304</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack. Gamla</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>128372956</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>128373425</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         <v>128372838</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128373388</v>
       </c>
       <c r="B2" t="n">
-        <v>91533</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128372905</v>
+        <v>128373425</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>440639</v>
+        <v>440620</v>
       </c>
       <c r="R3" t="n">
-        <v>6763304</v>
+        <v>6763308</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack. Gamla</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,54 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128372956</v>
+        <v>128372838</v>
       </c>
       <c r="B4" t="n">
-        <v>98643</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
+          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>440904</v>
+        <v>440534</v>
       </c>
       <c r="R4" t="n">
-        <v>6763627</v>
+        <v>6763273</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack. Kåda</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128373425</v>
+        <v>128372905</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1026,37 +1017,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440620</v>
+        <v>440639</v>
       </c>
       <c r="R5" t="n">
-        <v>6763308</v>
+        <v>6763304</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack. Gamla</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,50 +1123,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128372838</v>
+        <v>128372956</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skarpmyrrönningen, Skarpmyrrönningen, Dlr</t>
+          <t>Fagertjärnarna, Fagertjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>440534</v>
+        <v>440904</v>
       </c>
       <c r="R6" t="n">
-        <v>6763273</v>
+        <v>6763627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,12 +1212,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack. Kåda</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34715-2025 artfynd.xlsx
+++ b/artfynd/A 34715-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373388</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128373425</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128372838</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128372905</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,8 +1261,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128372956</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>